--- a/AAII_Financials/Quarterly/USB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/USB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>USB</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7148000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6684000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6760000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6729000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6474000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6391000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6419000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6276000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6270000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6132000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6219000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6485000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6320000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6714000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5974000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4728000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3825000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3418000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3355000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3409000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3382000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3341000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3479000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3573000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3672000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4116000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4255000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4437000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4451000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4351000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4311000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4123000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3948000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3791000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3730000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3704000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3519000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3393000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>3374000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3320000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7148000</v>
+      </c>
+      <c r="E10" s="3">
         <v>6684000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6760000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6729000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6474000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6391000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6419000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6276000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6270000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6132000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6219000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6485000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6320000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6714000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1471,33 +1490,33 @@
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>155000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>171000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>284000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>310000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>244000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1573,130 +1592,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>209000</v>
+      </c>
+      <c r="E15" s="3">
         <v>204000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>227000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>216000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>217000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>215000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>238000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>231000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>234000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>236000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>250000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>256000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>255000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>257000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-85000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-43000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-40000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-47000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-40000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-41000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-40000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-38000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-47000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-44000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-43000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-42000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-44000</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>-42000</v>
       </c>
       <c r="AE15" s="3">
         <v>-42000</v>
       </c>
       <c r="AF15" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="AG15" s="3">
         <v>-40000</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>-41000</v>
       </c>
       <c r="AH15" s="3">
         <v>-41000</v>
       </c>
       <c r="AI15" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>-40000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-39000</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>-44000</v>
       </c>
       <c r="AL15" s="3">
         <v>-44000</v>
       </c>
       <c r="AM15" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="AN15" s="3">
         <v>-43000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-44000</v>
-      </c>
-      <c r="AO15" s="3">
-        <v>-45000</v>
       </c>
       <c r="AP15" s="3">
         <v>-45000</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>-45000</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4314000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4155000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4101000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4072000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4057000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4109000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4172000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4062000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4072000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4158000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4892000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4085000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4100000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4151000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2873000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1263000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>701000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>357000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>219000</v>
-      </c>
-      <c r="V17" s="3">
-        <v>75000</v>
       </c>
       <c r="W17" s="3">
         <v>75000</v>
       </c>
       <c r="X17" s="3">
+        <v>75000</v>
+      </c>
+      <c r="Y17" s="3">
         <v>-549000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>745000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>981000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2209000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1886000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1443000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1523000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1511000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1469000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1376000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1215000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1078000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>964000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>890000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>888000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>820000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>758000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>761000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>752000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2834000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2529000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2659000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2657000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2417000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2282000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2247000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2214000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2198000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1974000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1327000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2400000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2220000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2563000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3101000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3465000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3124000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3061000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3136000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3334000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3307000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3890000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2734000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2592000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1463000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2230000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2812000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2914000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2940000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2882000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2935000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2908000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2870000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2827000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2840000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2816000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2699000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2635000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2613000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2568000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,252 +2056,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E20" s="3">
         <v>110000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>126000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>125000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>124000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>123000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>139000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>142000</v>
       </c>
       <c r="K20" s="3">
         <v>142000</v>
       </c>
       <c r="L20" s="3">
+        <v>142000</v>
+      </c>
+      <c r="M20" s="3">
         <v>146000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>156000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>161000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>159000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>160000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2000000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1168000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1176000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1106000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-999000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-736000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-768000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-998000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-814000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-659000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-704000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-791000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-965000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-530000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-663000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-796000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-782000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-626000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-671000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-783000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1529000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-658000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-636000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-650000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-573000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-486000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2929000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2623000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2760000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2748000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2510000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2374000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2346000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2303000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2290000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2064000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1421000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2495000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2316000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2660000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1276000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2425000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2073000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2087000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2262000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2724000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2663000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3014000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2054000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2066000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>890000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1568000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1977000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2511000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2402000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2206000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2274000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2400000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2314000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2157000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1429000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2275000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2179000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2102000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2157000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>2199000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2720000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2419000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2533000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2532000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2293000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2159000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2108000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2072000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2056000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1673000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1000000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1955000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1751000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2159000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1101000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2297000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1948000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1955000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2137000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2598000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2539000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2892000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1920000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1933000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>759000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1439000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1847000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2384000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2277000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2086000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2153000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2282000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2199000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2044000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1311000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2158000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2063000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1985000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2040000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2082000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>537000</v>
+      </c>
+      <c r="E24" s="3">
         <v>469000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>482000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>524000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>472000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>443000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>438000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>350000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>445000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>347000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>139000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>431000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>382000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>455000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>171000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>481000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>414000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>397000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>459000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>564000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>551000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>607000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>395000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>347000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>64000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>260000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>354000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>467000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>449000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>378000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>291000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>460000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>441000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>362000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>535000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>589000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>551000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>499000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>549000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>566000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2183000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1950000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2051000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2008000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1821000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1716000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1670000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1722000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1611000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1326000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>861000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1524000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1369000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1704000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>930000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1816000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1534000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1558000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1678000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2034000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1988000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2285000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1525000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1586000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>695000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1179000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1493000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1917000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1828000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1708000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1862000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1822000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1758000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1682000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>776000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1569000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1512000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1486000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1491000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1516000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2098000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1841000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1965000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1893000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1733000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1603000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1581000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1601000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1518000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1209000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>766000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1412000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1281000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1592000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>853000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1718000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1464000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1466000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1582000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1934000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1914000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2175000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1425000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1494000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>614000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1088000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1408000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1821000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1741000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1613000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1777000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1732000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1678000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1597000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>701000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1485000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1430000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1387000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1391000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1434000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>910000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-110000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-126000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-125000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-124000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-123000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-139000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-142000</v>
       </c>
       <c r="K32" s="3">
         <v>-142000</v>
       </c>
       <c r="L32" s="3">
+        <v>-142000</v>
+      </c>
+      <c r="M32" s="3">
         <v>-146000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-156000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-161000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-159000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-160000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2000000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1168000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1176000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1106000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>999000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>736000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>768000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>998000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>814000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>659000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>704000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>791000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>965000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>530000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>663000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>796000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>782000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>626000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>671000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>783000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1529000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>658000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>636000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>650000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>573000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>486000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2177000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1945000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2045000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2001000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1815000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1709000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1663000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1714000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1603000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1319000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>847000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1523000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1361000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1698000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>853000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1718000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1464000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1466000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1582000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1934000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1914000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2175000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1425000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1494000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>614000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1088000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1408000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1821000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1741000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1613000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1777000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1732000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1678000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1597000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1611000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1485000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1430000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1387000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1391000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1434000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2177000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1945000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2045000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2001000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1815000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1709000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1663000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1714000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1603000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1319000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>847000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1523000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1361000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1698000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>853000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1718000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1464000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1466000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1582000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1934000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1914000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2175000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1425000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1494000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>614000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1088000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1408000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1821000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1741000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1613000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1777000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1732000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1678000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1597000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1611000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1485000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1430000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1387000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1391000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1434000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>66491000</v>
+      </c>
+      <c r="E41" s="3">
         <v>48420000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>46839000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>66637000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>57807000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>50013000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>56449000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>73562000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>65832000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76985000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>61139000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>64354000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>70642000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>67228000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>53542000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41652000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39124000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>44303000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>28905000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>63904000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>44573000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43501000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>62580000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>44047000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>52392000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>46805000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>22405000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15272000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>16932000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>18115000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>21453000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>20082000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>19021000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>19246000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>19505000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>20540000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>28964000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>20319000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>15705000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>23664000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3888000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4246000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3701000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3690000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4201000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3270000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3458000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3488000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2711000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2673000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2865000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3122000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4101000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2980000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,8 +4524,11 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4479,8 +4571,8 @@
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4557,53 +4649,56 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E44" s="3">
         <v>40000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>43000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>44000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>43000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>42000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>39000</v>
       </c>
       <c r="J44" s="3">
         <v>39000</v>
       </c>
       <c r="K44" s="3">
+        <v>39000</v>
+      </c>
+      <c r="L44" s="3">
         <v>42000</v>
-      </c>
-      <c r="L44" s="3">
-        <v>45000</v>
       </c>
       <c r="M44" s="3">
         <v>45000</v>
       </c>
       <c r="N44" s="3">
+        <v>45000</v>
+      </c>
+      <c r="O44" s="3">
         <v>43000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>44000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>42000</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2714000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2648000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2585000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2713000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12819000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9041000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7501000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7490000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5554000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4878000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3548000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2585000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2422000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2773000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>76174000</v>
+      </c>
+      <c r="E46" s="3">
         <v>58282000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55757000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>75574000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>77158000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>64112000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>70073000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>87790000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>76721000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>86661000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>69851000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>72440000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>79570000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>75404000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,53 +5024,56 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>173296000</v>
+      </c>
+      <c r="E47" s="3">
         <v>179160000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>177032000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>175840000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>177942000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>173758000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>172997000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>169889000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>168913000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>162860000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>160629000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>159037000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>162599000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>159806000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5045,252 +5149,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3847000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3819000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3768000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3695000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3625000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3582000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3565000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3585000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3570000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3537000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3623000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3616000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3695000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3735000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3858000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3155000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3177000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3207000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3305000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3262000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3295000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3388000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3468000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3516000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3616000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3660000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3702000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3673000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3690000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3686000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2457000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2438000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2431000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2441000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2432000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2402000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2413000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2432000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2443000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2449000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18233000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17424000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17539000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17786000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17922000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17936000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18083000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18061000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18233000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18510000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18573000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18907000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19120000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19443000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19528000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14729000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14644000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>14444000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>14000000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>13524000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>13274000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>13367000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>12782000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>12543000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>12360000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>12465000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>12878000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>12615000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>12709000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>12888000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>12761000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>13074000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>12840000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>12828000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>12662000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>12563000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>12577000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>12661000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>12647000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>12244000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,53 +5649,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51713000</v>
+      </c>
+      <c r="E52" s="3">
         <v>50163000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>54519000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>47502000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>37017000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>42866000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>41351000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40540000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>44037000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>44964000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>44359000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>46023000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>43577000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>43143000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5655,8 +5774,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>725918000</v>
+      </c>
+      <c r="E54" s="3">
         <v>700998000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>692345000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>695357000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>686370000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>676489000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>678318000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>686469000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>680058000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>683606000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>663491000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>668039000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>680825000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>682377000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>674805000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>600973000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>591381000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>586517000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>573284000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>567495000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>558886000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>553375000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>553905000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>540455000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>546652000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>542909000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>495426000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>487671000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>481719000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>475775000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>467374000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>464607000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>461329000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>460119000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>462040000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>459227000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>463844000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>449522000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>445964000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>454134000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>532066000</v>
+      </c>
+      <c r="E57" s="3">
         <v>528178000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>522216000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>526149000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>518717000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>512525000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>518309000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>521131000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>523785000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>528063000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>512312000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>518358000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>521600000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>505339000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,53 +6239,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>41025000</v>
+      </c>
+      <c r="E58" s="3">
         <v>21011000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>36333000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>18580000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18764000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21086000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20729000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>27465000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>21381000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>22027000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20868000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>29414000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>39946000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>62126000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6231,8 +6364,11 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6275,62 +6411,62 @@
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>1500000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>1170000</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1234000</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>1342000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1344000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1381000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1396000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ59" s="3">
         <v>0</v>
@@ -6353,53 +6489,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>573091000</v>
+      </c>
+      <c r="E60" s="3">
         <v>549189000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>558549000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>544729000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>537481000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>533611000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>539038000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>548596000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>545166000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>550090000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>533180000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>547772000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>561546000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>567465000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,175 +6614,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58671000</v>
+      </c>
+      <c r="E61" s="3">
         <v>61361000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>46412000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>62535000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>64013000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>59859000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>58002000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>54839000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>52720000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>52693000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50480000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>43074000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>45283000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>42045000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>38329000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>32228000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>29408000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>32931000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>30955000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>35671000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>36360000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>37419000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>40063000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>42443000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>42579000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>52298000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>38825000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>39930000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>39627000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>39284000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>41340000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>40894000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>37172000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>33201000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>32259000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>34515000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>37814000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>35948000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>33323000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>37978000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26261000</v>
+      </c>
+      <c r="E62" s="3">
         <v>24201000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21733000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24295000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>22980000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22461000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22238000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23713000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25287000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24790000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24060000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>23615000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20512000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>19413000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6719,8 +6864,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>658023000</v>
+      </c>
+      <c r="E66" s="3">
         <v>634751000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>626694000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>631559000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>624474000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>615931000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>619278000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>627148000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>623173000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>627573000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>607720000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>614461000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>627341000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>628923000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>624039000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>553460000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>542776000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>535317000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>518366000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>513752000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>505847000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>501697000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>500810000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>487890000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>494802000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>491377000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>443573000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>434154000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>428806000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>423718000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>416345000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>414232000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>411701000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>410932000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>413000000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>410504000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>415524000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>401724000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>398666000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>406375000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7552,10 +7719,10 @@
         <v>6808000</v>
       </c>
       <c r="U70" s="3">
+        <v>6808000</v>
+      </c>
+      <c r="V70" s="3">
         <v>6371000</v>
-      </c>
-      <c r="V70" s="3">
-        <v>5968000</v>
       </c>
       <c r="W70" s="3">
         <v>5968000</v>
@@ -7564,10 +7731,10 @@
         <v>5968000</v>
       </c>
       <c r="Y70" s="3">
+        <v>5968000</v>
+      </c>
+      <c r="Z70" s="3">
         <v>5983000</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>5984000</v>
       </c>
       <c r="AA70" s="3">
         <v>5984000</v>
@@ -7594,7 +7761,7 @@
         <v>5984000</v>
       </c>
       <c r="AI70" s="3">
-        <v>5419000</v>
+        <v>5984000</v>
       </c>
       <c r="AJ70" s="3">
         <v>5419000</v>
@@ -7612,13 +7779,16 @@
         <v>5419000</v>
       </c>
       <c r="AO70" s="3">
-        <v>5501000</v>
+        <v>5419000</v>
       </c>
       <c r="AP70" s="3">
         <v>5501000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>5501000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>83241000</v>
+      </c>
+      <c r="E72" s="3">
         <v>81944000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>80906000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>79742000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>78652000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>77691000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>76863000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>76057000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>75231000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>74473000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>74026000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>74023000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>73355000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>72807000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>71901000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>71782000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>70772000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>69987000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>69201000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>68297000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>67039000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>65740000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>64188000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>63391000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>62526000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>62544000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>63186000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>62419000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>61252000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>60092000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>59065000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>57878000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>56742000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>55549000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>54142000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>53023000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>52033000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>51069000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>50151000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>49231000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>60624000</v>
+      </c>
+      <c r="E76" s="3">
         <v>58978000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>58385000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>56532000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>54630000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>53288000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>51770000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>52051000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>49612000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48760000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48498000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>46305000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>46211000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>46181000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43958000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>40705000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>41797000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>44392000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>48547000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>47775000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>47071000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>45710000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>47112000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>46581000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>45866000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>45548000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>45869000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>47533000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>46929000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>46073000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>45045000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>44391000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>44209000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>43768000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>43621000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>43304000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>42901000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>42379000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>41797000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>42258000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2177000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1945000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2045000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2001000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1815000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1709000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1663000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1714000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1603000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1319000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>847000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1523000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1361000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1698000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>853000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1718000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1464000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1466000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1582000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1934000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1914000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2175000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1425000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1494000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>614000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1088000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1408000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1821000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1741000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1613000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1777000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1732000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1678000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1597000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1611000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1485000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1430000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1387000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1391000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1434000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,43 +8961,44 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E83" s="3">
         <v>92000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>99000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>89000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>92000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>90000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>94000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>95000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>96000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>97000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>90000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>85000</v>
       </c>
       <c r="O83" s="3">
         <v>85000</v>
@@ -8809,76 +9007,76 @@
         <v>85000</v>
       </c>
       <c r="Q83" s="3">
+        <v>85000</v>
+      </c>
+      <c r="R83" s="3">
         <v>175000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>128000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>125000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>132000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>125000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>126000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>124000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>122000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>134000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>133000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>131000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>129000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>130000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>127000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>125000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>120000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>121000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>118000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>115000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>113000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>118000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>117000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>116000</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>117000</v>
       </c>
       <c r="AO83" s="3">
         <v>117000</v>
@@ -8886,8 +9084,11 @@
       <c r="AP83" s="3">
         <v>117000</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>117000</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4820000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1340000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2836000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3388000</v>
       </c>
-      <c r="G89" s="3">
-        <v>2031000</v>
-      </c>
       <c r="H89" s="3">
+        <v>1913000</v>
+      </c>
+      <c r="I89" s="3">
         <v>-308000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4843000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>972000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2874000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2661000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>416000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3873000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3316000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>842000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6888000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3505000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2249000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8477000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>703000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2647000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5583000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>937000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1069000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3284000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-853000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2354000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-62000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3046000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>609000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1296000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2650000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3225000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3255000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1434000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-169000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1862000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1589000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3190000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2098000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>554000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6377000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5351000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16850000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>230000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1370000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2548000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12875000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1622000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8328000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4953000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1800000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>5636000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>6546000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>4943000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>34577000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7561000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12152000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7364000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-41718000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>9587000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5890000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19466000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>6410000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3855000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>4264000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-22259000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-189000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9499000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5328000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-6544000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4757000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2051000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2251000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>82000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2806000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2506000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-5093000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1721000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2717000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-5147000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,76 +10426,77 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E96" s="3">
         <v>816000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>813000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>784000</v>
       </c>
       <c r="G96" s="3">
         <v>784000</v>
       </c>
       <c r="H96" s="3">
+        <v>784000</v>
+      </c>
+      <c r="I96" s="3">
         <v>787000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>785000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>768000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>769000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>770000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>751000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>740000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>739000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>740000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-716000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-687000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-686000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-687000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-685000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-626000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-631000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-637000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-635000</v>
       </c>
       <c r="Z96" s="3">
         <v>-635000</v>
@@ -10272,52 +10505,55 @@
         <v>-635000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-635000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-647000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-663000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-589000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-594000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-597000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-603000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-493000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-497000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-499000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-502000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-472000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-476000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-478000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-479000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-440000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,142 +10924,148 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>19695000</v>
+      </c>
+      <c r="E100" s="3">
         <v>5673000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6439000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5212000</v>
       </c>
-      <c r="G100" s="3">
-        <v>7133000</v>
-      </c>
       <c r="H100" s="3">
+        <v>6765000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-3896000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8701000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5136000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5699000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>18085000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5378000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-15797000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5448000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6901000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-29575000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6584000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4724000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>14285000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6016000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>7097000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1379000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-550000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>13192000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-7774000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2176000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>44305000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>7384000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>4793000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>3536000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1910000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3478000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-113000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1229000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1775000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1940000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-7780000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>12149000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>3145000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-7340000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>14219000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E101" s="3">
         <v>263000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-327000</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>5</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18071000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1530000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19747000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8830000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7794000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6489000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17060000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7730000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11153000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15793000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3162000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6288000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4414000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12686000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>11890000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2528000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5179000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15398000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-34999000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>19331000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1072000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-19079000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18533000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-8345000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5587000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>24400000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>7133000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1660000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1183000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3338000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1371000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1061000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-225000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-259000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1035000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-8424000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>8645000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>4614000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-7959000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>9626000</v>
       </c>
     </row>
